--- a/planificacion_stomasense.xlsx
+++ b/planificacion_stomasense.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rchaitanya\Desktop\OnGoing\Agriculture-AI\Tracker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47E8F4AF-483C-49BB-9671-F9C146C410B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE46E9BD-B755-4757-80F0-02FB56BD3339}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19180" yWindow="110" windowWidth="19180" windowHeight="10060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planificación" sheetId="1" r:id="rId1"/>
@@ -1198,9 +1198,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:N47"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="32" customWidth="1"/>
     <col min="4" max="4" width="20" customWidth="1"/>
@@ -1209,13 +1209,13 @@
     <col min="7" max="7" width="20" customWidth="1"/>
     <col min="8" max="9" width="13" customWidth="1"/>
     <col min="10" max="10" width="7" customWidth="1"/>
-    <col min="11" max="11" width="10.81640625" customWidth="1"/>
+    <col min="11" max="11" width="10.85546875" customWidth="1"/>
     <col min="12" max="12" width="14" customWidth="1"/>
     <col min="13" max="13" width="30" customWidth="1"/>
     <col min="14" max="14" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="32.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
@@ -1233,7 +1233,7 @@
       <c r="M1" s="16"/>
       <c r="N1" s="16"/>
     </row>
-    <row r="2" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="15" t="s">
         <v>1</v>
       </c>
@@ -1251,7 +1251,7 @@
       <c r="M2" s="16"/>
       <c r="N2" s="16"/>
     </row>
-    <row r="3" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
@@ -1295,7 +1295,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="10">
         <v>1</v>
       </c>
@@ -1321,11 +1321,11 @@
         <v>46098</v>
       </c>
       <c r="I4" s="12">
-        <v>46108</v>
+        <v>46139</v>
       </c>
       <c r="J4" s="13">
         <f t="shared" ref="J4:J9" si="0">+I4-H4</f>
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="K4" s="10">
         <v>90</v>
@@ -1338,7 +1338,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="10">
         <v>2</v>
       </c>
@@ -1371,7 +1371,7 @@
         <v>10</v>
       </c>
       <c r="K5" s="10">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="L5" s="14" t="s">
         <v>22</v>
@@ -1381,7 +1381,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="10">
         <v>3</v>
       </c>
@@ -1407,11 +1407,11 @@
         <v>46091</v>
       </c>
       <c r="I6" s="12">
-        <v>46108</v>
+        <v>46139</v>
       </c>
       <c r="J6" s="13">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="K6" s="10">
         <v>85</v>
@@ -1424,7 +1424,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="10">
         <v>4</v>
       </c>
@@ -1450,11 +1450,11 @@
         <v>46091</v>
       </c>
       <c r="I7" s="12">
-        <v>46108</v>
+        <v>46139</v>
       </c>
       <c r="J7" s="13">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="K7" s="10">
         <v>85</v>
@@ -1467,7 +1467,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="10">
         <v>5</v>
       </c>
@@ -1510,7 +1510,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="10">
         <v>6</v>
       </c>
@@ -1553,7 +1553,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="10">
         <v>7</v>
       </c>
@@ -1595,7 +1595,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="10">
         <v>8</v>
       </c>
@@ -1637,7 +1637,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="10">
         <v>8</v>
       </c>
@@ -1679,7 +1679,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="10">
         <v>14</v>
       </c>
@@ -1721,7 +1721,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="10">
         <v>15</v>
       </c>
@@ -1763,7 +1763,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="10">
         <v>16</v>
       </c>
@@ -1805,7 +1805,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="10">
         <v>17</v>
       </c>
@@ -1847,7 +1847,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="10">
         <v>18</v>
       </c>
@@ -1889,7 +1889,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="10">
         <v>19</v>
       </c>
@@ -1931,7 +1931,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="10">
         <v>20</v>
       </c>
@@ -1973,7 +1973,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="10">
         <v>21</v>
       </c>
@@ -2015,7 +2015,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10">
         <v>22</v>
       </c>
@@ -2057,7 +2057,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="10">
         <v>23</v>
       </c>
@@ -2099,7 +2099,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="10">
         <v>24</v>
       </c>
@@ -2141,7 +2141,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="10">
         <v>25</v>
       </c>
@@ -2183,7 +2183,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="10">
         <v>26</v>
       </c>
@@ -2225,7 +2225,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="10">
         <v>27</v>
       </c>
@@ -2267,7 +2267,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="10">
         <v>26</v>
       </c>
@@ -2309,7 +2309,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="10">
         <v>25</v>
       </c>
@@ -2351,7 +2351,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="10">
         <v>24</v>
       </c>
@@ -2393,7 +2393,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="10">
         <v>23</v>
       </c>
@@ -2435,7 +2435,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="10">
         <v>22</v>
       </c>
@@ -2477,7 +2477,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="10">
         <v>21</v>
       </c>
@@ -2519,7 +2519,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="33" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="10">
         <v>20</v>
       </c>
@@ -2561,7 +2561,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="34" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="10">
         <v>19</v>
       </c>
@@ -2603,7 +2603,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="35" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="10">
         <v>18</v>
       </c>
@@ -2645,7 +2645,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="36" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="10">
         <v>17</v>
       </c>
@@ -2687,7 +2687,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="37" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="10">
         <v>16</v>
       </c>
@@ -2729,7 +2729,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="38" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="10">
         <v>15</v>
       </c>
@@ -2771,7 +2771,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="39" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="10">
         <v>14</v>
       </c>
@@ -2813,7 +2813,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="40" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="10">
         <v>13</v>
       </c>
@@ -2855,7 +2855,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="41" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="10">
         <v>12</v>
       </c>
@@ -2897,7 +2897,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="42" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="10">
         <v>11</v>
       </c>
@@ -2939,7 +2939,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="43" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="10">
         <v>10</v>
       </c>
@@ -2981,7 +2981,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="44" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="10">
         <v>9</v>
       </c>
@@ -3025,7 +3025,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="45" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="10">
         <v>8</v>
       </c>
@@ -3067,7 +3067,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="46" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="10">
         <v>7</v>
       </c>
@@ -3109,7 +3109,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="47" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="10">
         <v>6</v>
       </c>
@@ -3175,13 +3175,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>144</v>
       </c>
@@ -3189,7 +3189,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>34</v>
       </c>
@@ -3197,7 +3197,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>22</v>
       </c>
@@ -3205,7 +3205,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>148</v>
       </c>
@@ -3213,7 +3213,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
         <v>150</v>
       </c>
@@ -3221,7 +3221,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>152</v>
       </c>

--- a/planificacion_stomasense.xlsx
+++ b/planificacion_stomasense.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rchaitanya\Desktop\OnGoing\Agriculture-AI\Tracker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE46E9BD-B755-4757-80F0-02FB56BD3339}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67686260-DE4F-4DB7-BB4D-7469D500C3F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -506,7 +506,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -553,6 +553,12 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="9">
@@ -625,7 +631,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -675,6 +681,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1373,7 +1382,7 @@
       <c r="K5" s="10">
         <v>100</v>
       </c>
-      <c r="L5" s="14" t="s">
+      <c r="L5" s="18" t="s">
         <v>22</v>
       </c>
       <c r="M5" s="11"/>
@@ -1621,7 +1630,7 @@
         <v>46098</v>
       </c>
       <c r="I11" s="12">
-        <v>46105</v>
+        <v>46136</v>
       </c>
       <c r="J11" s="10">
         <v>8</v>
@@ -1663,7 +1672,7 @@
         <v>46098</v>
       </c>
       <c r="I12" s="12">
-        <v>46105</v>
+        <v>46136</v>
       </c>
       <c r="J12" s="10">
         <v>8</v>

--- a/planificacion_stomasense.xlsx
+++ b/planificacion_stomasense.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rchaitanya\Desktop\OnGoing\Agriculture-AI\Tracker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE46E9BD-B755-4757-80F0-02FB56BD3339}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83B732BE-1F19-4C7E-9509-3443B354A8C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1621,7 +1621,7 @@
         <v>46098</v>
       </c>
       <c r="I11" s="12">
-        <v>46105</v>
+        <v>46136</v>
       </c>
       <c r="J11" s="10">
         <v>8</v>
@@ -1663,7 +1663,7 @@
         <v>46098</v>
       </c>
       <c r="I12" s="12">
-        <v>46105</v>
+        <v>46136</v>
       </c>
       <c r="J12" s="10">
         <v>8</v>

--- a/planificacion_stomasense.xlsx
+++ b/planificacion_stomasense.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rchaitanya\Desktop\OnGoing\Agriculture-AI\Tracker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83B732BE-1F19-4C7E-9509-3443B354A8C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{228522E5-2F5B-45DB-9C94-6C51E9DD2247}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Leyenda" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planificación!$A$3:$N$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planificación!$A$3:$N$48</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="155">
   <si>
     <t>STOMASENSE – ROADMAP DE PRIORIDADES 2026</t>
   </si>
@@ -97,9 +97,6 @@
     <t>Web</t>
   </si>
   <si>
-    <t>Backlog Stoma Sense</t>
-  </si>
-  <si>
     <t>Revisión de issues reportados en módulo de teledetección (NDVI+, Hydro Plus, Smart Growth, Weed Detection) + metricas</t>
   </si>
   <si>
@@ -500,13 +497,19 @@
   </si>
   <si>
     <t>Tarea en fase de revisión/aprobación</t>
+  </si>
+  <si>
+    <t>Product improvement Log Review Stoma Sense</t>
+  </si>
+  <si>
+    <t>Additional Feature Requests and Enhancements</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -553,6 +556,18 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="9">
@@ -625,7 +640,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -675,6 +690,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -889,8 +922,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5DBEE949-8DB6-4AB6-B75B-8C818D89B4ED}" name="Tabla1" displayName="Tabla1" ref="A3:N47" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15" tableBorderDxfId="14">
-  <autoFilter ref="A3:N47" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5DBEE949-8DB6-4AB6-B75B-8C818D89B4ED}" name="Tabla1" displayName="Tabla1" ref="A3:N48" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15" tableBorderDxfId="14">
+  <autoFilter ref="A3:N48" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{A792A13F-07B2-4DE9-AECE-E0C5BB01A358}" name="ID" dataDxfId="13"/>
     <tableColumn id="2" xr3:uid="{9F2A0000-8EF2-487A-9FDD-858EFAE9F037}" name="Bloque" dataDxfId="12"/>
@@ -1197,7 +1230,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:N47"/>
+  <dimension ref="A1:N48"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.7109375" bestFit="1" customWidth="1"/>
@@ -1308,14 +1341,14 @@
       <c r="D4" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="F4" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="G4" s="11" t="s">
         <v>20</v>
-      </c>
-      <c r="G4" s="11" t="s">
-        <v>21</v>
       </c>
       <c r="H4" s="12">
         <v>46098</v>
@@ -1331,11 +1364,11 @@
         <v>90</v>
       </c>
       <c r="L4" s="14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M4" s="11"/>
       <c r="N4" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -1352,13 +1385,13 @@
         <v>18</v>
       </c>
       <c r="E5" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="11" t="s">
-        <v>25</v>
-      </c>
       <c r="G5" s="11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H5" s="12">
         <v>46091</v>
@@ -1374,11 +1407,11 @@
         <v>100</v>
       </c>
       <c r="L5" s="14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M5" s="11"/>
       <c r="N5" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -1395,33 +1428,33 @@
         <v>18</v>
       </c>
       <c r="E6" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="F6" s="11" t="s">
+      <c r="G6" s="11" t="s">
         <v>27</v>
-      </c>
-      <c r="G6" s="11" t="s">
-        <v>28</v>
       </c>
       <c r="H6" s="12">
         <v>46091</v>
       </c>
       <c r="I6" s="12">
-        <v>46139</v>
+        <v>46127</v>
       </c>
       <c r="J6" s="13">
         <f t="shared" si="0"/>
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="K6" s="10">
         <v>85</v>
       </c>
       <c r="L6" s="14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M6" s="11"/>
       <c r="N6" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -1438,33 +1471,33 @@
         <v>18</v>
       </c>
       <c r="E7" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="F7" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="F7" s="11" t="s">
+      <c r="G7" s="11" t="s">
         <v>30</v>
-      </c>
-      <c r="G7" s="11" t="s">
-        <v>31</v>
       </c>
       <c r="H7" s="12">
         <v>46091</v>
       </c>
       <c r="I7" s="12">
-        <v>46139</v>
+        <v>46115</v>
       </c>
       <c r="J7" s="13">
         <f t="shared" si="0"/>
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="K7" s="10">
         <v>85</v>
       </c>
-      <c r="L7" s="14" t="s">
-        <v>22</v>
+      <c r="L7" s="19" t="s">
+        <v>21</v>
       </c>
       <c r="M7" s="11"/>
       <c r="N7" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -1481,33 +1514,33 @@
         <v>18</v>
       </c>
       <c r="E8" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="F8" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="F8" s="11" t="s">
-        <v>33</v>
-      </c>
       <c r="G8" s="11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H8" s="12">
-        <v>46098</v>
+        <v>46106</v>
       </c>
       <c r="I8" s="12">
-        <v>46132</v>
+        <v>46117</v>
       </c>
       <c r="J8" s="13">
         <f t="shared" si="0"/>
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="K8" s="10">
         <v>85</v>
       </c>
-      <c r="L8" s="14" t="s">
-        <v>34</v>
+      <c r="L8" s="19" t="s">
+        <v>21</v>
       </c>
       <c r="M8" s="11"/>
       <c r="N8" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -1524,13 +1557,13 @@
         <v>18</v>
       </c>
       <c r="E9" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="F9" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="F9" s="11" t="s">
-        <v>36</v>
-      </c>
       <c r="G9" s="11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H9" s="12">
         <v>46113</v>
@@ -1543,14 +1576,14 @@
         <v>14</v>
       </c>
       <c r="K9" s="10">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="L9" s="14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M9" s="11"/>
       <c r="N9" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -1567,13 +1600,13 @@
         <v>18</v>
       </c>
       <c r="E10" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="F10" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="F10" s="11" t="s">
-        <v>38</v>
-      </c>
       <c r="G10" s="11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H10" s="12">
         <v>46113</v>
@@ -1585,37 +1618,37 @@
         <v>19</v>
       </c>
       <c r="K10" s="10">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="L10" s="14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M10" s="11"/>
       <c r="N10" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="10">
         <v>8</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="D11" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="E11" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="E11" s="11" t="s">
+      <c r="F11" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="F11" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="G11" s="11" t="s">
-        <v>31</v>
+      <c r="G11" s="18" t="s">
+        <v>30</v>
       </c>
       <c r="H11" s="12">
         <v>46098</v>
@@ -1629,545 +1662,545 @@
       <c r="K11" s="10">
         <v>70</v>
       </c>
-      <c r="L11" s="14" t="s">
-        <v>22</v>
+      <c r="L11" s="19" t="s">
+        <v>21</v>
       </c>
       <c r="M11" s="11"/>
       <c r="N11" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="10">
+      <c r="A12" s="20">
         <v>8</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="D12" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="E12" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="F12" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="G12" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="H12" s="12">
+      <c r="E12" s="23" t="s">
+        <v>154</v>
+      </c>
+      <c r="F12" s="23" t="s">
+        <v>154</v>
+      </c>
+      <c r="G12" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="H12" s="22">
         <v>46098</v>
       </c>
-      <c r="I12" s="12">
-        <v>46136</v>
-      </c>
-      <c r="J12" s="10">
+      <c r="I12" s="22">
+        <v>46122</v>
+      </c>
+      <c r="J12" s="20">
         <v>8</v>
       </c>
-      <c r="K12" s="10">
-        <v>0</v>
-      </c>
-      <c r="L12" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="M12" s="11"/>
+      <c r="K12" s="20">
+        <v>80</v>
+      </c>
+      <c r="L12" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="M12" s="21"/>
       <c r="N12" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="10">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B13" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="H13" s="12">
         <v>46098</v>
       </c>
       <c r="I13" s="12">
-        <v>46122</v>
+        <v>46136</v>
       </c>
       <c r="J13" s="10">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="K13" s="10">
         <v>0</v>
       </c>
       <c r="L13" s="14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M13" s="11"/>
       <c r="N13" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="10">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B14" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C14" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="E14" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="E14" s="11" t="s">
-        <v>49</v>
-      </c>
       <c r="F14" s="11" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="H14" s="12">
-        <v>46113</v>
+        <v>46098</v>
       </c>
       <c r="I14" s="12">
-        <v>46132</v>
+        <v>46122</v>
       </c>
       <c r="J14" s="10">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K14" s="10">
         <v>0</v>
       </c>
-      <c r="L14" s="11" t="s">
-        <v>34</v>
+      <c r="L14" s="14" t="s">
+        <v>21</v>
       </c>
       <c r="M14" s="11"/>
       <c r="N14" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="10">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B15" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C15" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="D15" s="11" t="s">
-        <v>46</v>
-      </c>
       <c r="E15" s="11" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H15" s="12">
-        <v>46127</v>
+        <v>46113</v>
       </c>
       <c r="I15" s="12">
-        <v>46152</v>
+        <v>46132</v>
       </c>
       <c r="J15" s="10">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="K15" s="10">
         <v>0</v>
       </c>
       <c r="L15" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M15" s="11"/>
       <c r="N15" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="10">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B16" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C16" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="D16" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="D16" s="11" t="s">
-        <v>46</v>
-      </c>
       <c r="E16" s="11" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="H16" s="12">
-        <v>46153</v>
+        <v>46127</v>
       </c>
       <c r="I16" s="12">
-        <v>46167</v>
+        <v>46152</v>
       </c>
       <c r="J16" s="10">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="K16" s="10">
         <v>0</v>
       </c>
       <c r="L16" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M16" s="11"/>
       <c r="N16" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="10">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B17" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C17" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="D17" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="D17" s="11" t="s">
-        <v>46</v>
-      </c>
       <c r="E17" s="11" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H17" s="12">
-        <v>46168</v>
+        <v>46153</v>
       </c>
       <c r="I17" s="12">
-        <v>46173</v>
+        <v>46167</v>
       </c>
       <c r="J17" s="10">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="K17" s="10">
         <v>0</v>
       </c>
       <c r="L17" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M17" s="11"/>
       <c r="N17" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="10">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>61</v>
+        <v>16</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>21</v>
+        <v>59</v>
       </c>
       <c r="H18" s="12">
-        <v>46143</v>
+        <v>46168</v>
       </c>
       <c r="I18" s="12">
-        <v>46162</v>
+        <v>46173</v>
       </c>
       <c r="J18" s="10">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="K18" s="10">
         <v>0</v>
       </c>
       <c r="L18" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M18" s="11"/>
       <c r="N18" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="10">
+        <v>19</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="G19" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="B19" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="D19" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="E19" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="F19" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="G19" s="11" t="s">
-        <v>68</v>
-      </c>
       <c r="H19" s="12">
-        <v>46163</v>
+        <v>46143</v>
       </c>
       <c r="I19" s="12">
-        <v>46188</v>
+        <v>46162</v>
       </c>
       <c r="J19" s="10">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="K19" s="10">
         <v>0</v>
       </c>
       <c r="L19" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M19" s="11"/>
       <c r="N19" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="10">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B20" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="C20" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="C20" s="11" t="s">
+      <c r="D20" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="D20" s="11" t="s">
-        <v>63</v>
-      </c>
       <c r="E20" s="11" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H20" s="12">
-        <v>46174</v>
+        <v>46163</v>
       </c>
       <c r="I20" s="12">
-        <v>46203</v>
+        <v>46188</v>
       </c>
       <c r="J20" s="10">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="K20" s="10">
         <v>0</v>
       </c>
       <c r="L20" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M20" s="11"/>
       <c r="N20" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B21" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="C21" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="C21" s="11" t="s">
+      <c r="D21" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="D21" s="11" t="s">
-        <v>63</v>
-      </c>
       <c r="E21" s="11" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H21" s="12">
-        <v>46188</v>
+        <v>46174</v>
       </c>
       <c r="I21" s="12">
-        <v>46218</v>
+        <v>46203</v>
       </c>
       <c r="J21" s="10">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K21" s="10">
         <v>0</v>
       </c>
       <c r="L21" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M21" s="11"/>
       <c r="N21" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="10">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B22" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="C22" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="C22" s="11" t="s">
+      <c r="D22" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="D22" s="11" t="s">
-        <v>63</v>
-      </c>
       <c r="E22" s="11" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H22" s="12">
-        <v>46174</v>
+        <v>46188</v>
       </c>
       <c r="I22" s="12">
         <v>46218</v>
       </c>
       <c r="J22" s="10">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="K22" s="10">
         <v>0</v>
       </c>
       <c r="L22" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M22" s="11"/>
       <c r="N22" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="10">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B23" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="C23" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="C23" s="11" t="s">
+      <c r="D23" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="D23" s="11" t="s">
-        <v>63</v>
-      </c>
       <c r="E23" s="11" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G23" s="11" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="H23" s="12">
-        <v>46219</v>
+        <v>46174</v>
       </c>
       <c r="I23" s="12">
-        <v>46249</v>
+        <v>46218</v>
       </c>
       <c r="J23" s="10">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="K23" s="10">
         <v>0</v>
       </c>
       <c r="L23" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M23" s="11"/>
       <c r="N23" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="10">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B24" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="C24" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="C24" s="11" t="s">
+      <c r="D24" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="D24" s="11" t="s">
-        <v>63</v>
-      </c>
       <c r="E24" s="11" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G24" s="11" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H24" s="12">
-        <v>46250</v>
+        <v>46219</v>
       </c>
       <c r="I24" s="12">
-        <v>46280</v>
+        <v>46249</v>
       </c>
       <c r="J24" s="10">
         <v>31</v>
@@ -2176,40 +2209,40 @@
         <v>0</v>
       </c>
       <c r="L24" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M24" s="11"/>
       <c r="N24" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="10">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B25" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="C25" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="C25" s="11" t="s">
-        <v>81</v>
-      </c>
       <c r="D25" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="G25" s="11" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="H25" s="12">
-        <v>46143</v>
+        <v>46250</v>
       </c>
       <c r="I25" s="12">
-        <v>46173</v>
+        <v>46280</v>
       </c>
       <c r="J25" s="10">
         <v>31</v>
@@ -2218,124 +2251,124 @@
         <v>0</v>
       </c>
       <c r="L25" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M25" s="11"/>
       <c r="N25" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="10">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C26" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="E26" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="D26" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="E26" s="11" t="s">
-        <v>84</v>
-      </c>
       <c r="F26" s="11" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="G26" s="11" t="s">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="H26" s="12">
-        <v>46174</v>
+        <v>46143</v>
       </c>
       <c r="I26" s="12">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="J26" s="10">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K26" s="10">
         <v>0</v>
       </c>
       <c r="L26" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M26" s="11"/>
       <c r="N26" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="10">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="G27" s="11" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="H27" s="12">
-        <v>46204</v>
+        <v>46174</v>
       </c>
       <c r="I27" s="12">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="J27" s="10">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K27" s="10">
         <v>0</v>
       </c>
       <c r="L27" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M27" s="11"/>
       <c r="N27" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="10">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="G28" s="11" t="s">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="H28" s="12">
-        <v>46235</v>
+        <v>46204</v>
       </c>
       <c r="I28" s="12">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="J28" s="10">
         <v>31</v>
@@ -2344,376 +2377,376 @@
         <v>0</v>
       </c>
       <c r="L28" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M28" s="11"/>
       <c r="N28" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="10">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="F29" s="11" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="G29" s="11" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H29" s="12">
-        <v>46266</v>
+        <v>46235</v>
       </c>
       <c r="I29" s="12">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="J29" s="10">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K29" s="10">
         <v>0</v>
       </c>
       <c r="L29" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M29" s="11"/>
       <c r="N29" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="30" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="10">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="G30" s="11" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="H30" s="12">
-        <v>46157</v>
+        <v>46266</v>
       </c>
       <c r="I30" s="12">
-        <v>46188</v>
+        <v>46295</v>
       </c>
       <c r="J30" s="10">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K30" s="10">
         <v>0</v>
       </c>
       <c r="L30" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M30" s="11"/>
       <c r="N30" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="31" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="10">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C31" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="D31" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="E31" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="D31" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="E31" s="11" t="s">
-        <v>99</v>
-      </c>
       <c r="F31" s="11" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="G31" s="11" t="s">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="H31" s="12">
-        <v>46189</v>
+        <v>46157</v>
       </c>
       <c r="I31" s="12">
-        <v>46218</v>
+        <v>46188</v>
       </c>
       <c r="J31" s="10">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K31" s="10">
         <v>0</v>
       </c>
       <c r="L31" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M31" s="11"/>
       <c r="N31" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="10">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="G32" s="11" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="H32" s="12">
-        <v>46219</v>
+        <v>46189</v>
       </c>
       <c r="I32" s="12">
-        <v>46265</v>
+        <v>46218</v>
       </c>
       <c r="J32" s="10">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="K32" s="10">
         <v>0</v>
       </c>
       <c r="L32" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M32" s="11"/>
       <c r="N32" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="10">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="G33" s="11" t="s">
-        <v>105</v>
+        <v>67</v>
       </c>
       <c r="H33" s="12">
-        <v>46266</v>
+        <v>46219</v>
       </c>
       <c r="I33" s="12">
-        <v>46310</v>
+        <v>46265</v>
       </c>
       <c r="J33" s="10">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K33" s="10">
         <v>0</v>
       </c>
       <c r="L33" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M33" s="11"/>
       <c r="N33" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="34" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="10">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>107</v>
+        <v>62</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="G34" s="11" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="H34" s="12">
-        <v>46157</v>
+        <v>46266</v>
       </c>
       <c r="I34" s="12">
-        <v>46174</v>
+        <v>46310</v>
       </c>
       <c r="J34" s="10">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="K34" s="10">
         <v>0</v>
       </c>
       <c r="L34" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M34" s="11"/>
       <c r="N34" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="35" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="10">
+        <v>19</v>
+      </c>
+      <c r="B35" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="D35" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="E35" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="F35" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="G35" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="H35" s="12">
+        <v>46157</v>
+      </c>
+      <c r="I35" s="12">
+        <v>46174</v>
+      </c>
+      <c r="J35" s="10">
         <v>18</v>
       </c>
-      <c r="B35" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="C35" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="D35" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="E35" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="F35" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="G35" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="H35" s="12">
-        <v>46174</v>
-      </c>
-      <c r="I35" s="12">
-        <v>46203</v>
-      </c>
-      <c r="J35" s="10">
-        <v>30</v>
-      </c>
       <c r="K35" s="10">
         <v>0</v>
       </c>
       <c r="L35" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M35" s="11"/>
       <c r="N35" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="36" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="10">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C36" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="D36" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="D36" s="11" t="s">
-        <v>107</v>
-      </c>
       <c r="E36" s="11" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="G36" s="11" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="H36" s="12">
-        <v>46204</v>
+        <v>46174</v>
       </c>
       <c r="I36" s="12">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="J36" s="10">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K36" s="10">
         <v>0</v>
       </c>
       <c r="L36" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M36" s="11"/>
       <c r="N36" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="37" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="10">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C37" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="D37" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="D37" s="11" t="s">
-        <v>107</v>
-      </c>
       <c r="E37" s="11" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="G37" s="11" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="H37" s="12">
-        <v>46235</v>
+        <v>46204</v>
       </c>
       <c r="I37" s="12">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="J37" s="10">
         <v>31</v>
@@ -2722,378 +2755,378 @@
         <v>0</v>
       </c>
       <c r="L37" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M37" s="11"/>
       <c r="N37" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="38" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="10">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C38" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="D38" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="D38" s="11" t="s">
-        <v>107</v>
-      </c>
       <c r="E38" s="11" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G38" s="11" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H38" s="12">
-        <v>46266</v>
+        <v>46235</v>
       </c>
       <c r="I38" s="12">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="J38" s="10">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K38" s="10">
         <v>0</v>
       </c>
       <c r="L38" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M38" s="11"/>
       <c r="N38" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="39" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="10">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G39" s="11" t="s">
-        <v>31</v>
+        <v>93</v>
       </c>
       <c r="H39" s="12">
-        <v>46174</v>
+        <v>46266</v>
       </c>
       <c r="I39" s="12">
-        <v>46193</v>
+        <v>46295</v>
       </c>
       <c r="J39" s="10">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K39" s="10">
         <v>0</v>
       </c>
       <c r="L39" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M39" s="11"/>
       <c r="N39" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="40" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="10">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C40" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="D40" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="E40" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="D40" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="E40" s="11" t="s">
-        <v>122</v>
-      </c>
       <c r="F40" s="11" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="G40" s="11" t="s">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="H40" s="12">
-        <v>46194</v>
+        <v>46174</v>
       </c>
       <c r="I40" s="12">
-        <v>46223</v>
+        <v>46193</v>
       </c>
       <c r="J40" s="10">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="K40" s="10">
         <v>0</v>
       </c>
       <c r="L40" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M40" s="11"/>
       <c r="N40" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="41" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="10">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="G41" s="11" t="s">
-        <v>126</v>
+        <v>79</v>
       </c>
       <c r="H41" s="12">
-        <v>46224</v>
+        <v>46194</v>
       </c>
       <c r="I41" s="12">
-        <v>46254</v>
+        <v>46223</v>
       </c>
       <c r="J41" s="10">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K41" s="10">
         <v>0</v>
       </c>
       <c r="L41" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M41" s="11"/>
       <c r="N41" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="G42" s="11" t="s">
-        <v>94</v>
+        <v>125</v>
       </c>
       <c r="H42" s="12">
-        <v>46255</v>
+        <v>46224</v>
       </c>
       <c r="I42" s="12">
-        <v>46295</v>
+        <v>46254</v>
       </c>
       <c r="J42" s="10">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="K42" s="10">
         <v>0</v>
       </c>
       <c r="L42" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M42" s="11"/>
       <c r="N42" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="43" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="10">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>130</v>
+        <v>106</v>
       </c>
       <c r="E43" s="11" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="F43" s="11" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="G43" s="11" t="s">
-        <v>133</v>
+        <v>93</v>
       </c>
       <c r="H43" s="12">
-        <v>46143</v>
+        <v>46255</v>
       </c>
       <c r="I43" s="12">
-        <v>46167</v>
+        <v>46295</v>
       </c>
       <c r="J43" s="10">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="K43" s="10">
         <v>0</v>
       </c>
       <c r="L43" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M43" s="11"/>
       <c r="N43" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="44" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C44" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="D44" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="D44" s="11" t="s">
+      <c r="E44" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="E44" s="11" t="s">
-        <v>134</v>
-      </c>
       <c r="F44" s="11" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="G44" s="11" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="H44" s="12">
-        <v>46168</v>
+        <v>46143</v>
       </c>
       <c r="I44" s="12">
-        <v>46218</v>
+        <v>46167</v>
       </c>
       <c r="J44" s="10">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="K44" s="10">
         <v>0</v>
       </c>
       <c r="L44" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="M44" s="11" t="s">
-        <v>137</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="M44" s="11"/>
       <c r="N44" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="45" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B45" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C45" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="D45" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="D45" s="11" t="s">
-        <v>130</v>
-      </c>
       <c r="E45" s="11" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="G45" s="11" t="s">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="H45" s="12">
-        <v>46219</v>
+        <v>46168</v>
       </c>
       <c r="I45" s="12">
-        <v>46249</v>
+        <v>46218</v>
       </c>
       <c r="J45" s="10">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="K45" s="10">
         <v>0</v>
       </c>
       <c r="L45" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="M45" s="11"/>
+        <v>33</v>
+      </c>
+      <c r="M45" s="11" t="s">
+        <v>136</v>
+      </c>
       <c r="N45" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="46" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B46" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C46" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="D46" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="D46" s="11" t="s">
-        <v>130</v>
-      </c>
       <c r="E46" s="11" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="G46" s="11" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="H46" s="12">
-        <v>46250</v>
+        <v>46219</v>
       </c>
       <c r="I46" s="12">
-        <v>46280</v>
+        <v>46249</v>
       </c>
       <c r="J46" s="10">
         <v>31</v>
@@ -3102,53 +3135,95 @@
         <v>0</v>
       </c>
       <c r="L46" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M46" s="11"/>
       <c r="N46" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="47" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C47" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="D47" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="D47" s="11" t="s">
-        <v>130</v>
-      </c>
       <c r="E47" s="11" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F47" s="11" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="G47" s="11" t="s">
-        <v>54</v>
+        <v>90</v>
       </c>
       <c r="H47" s="12">
-        <v>46281</v>
+        <v>46250</v>
       </c>
       <c r="I47" s="12">
-        <v>46310</v>
+        <v>46280</v>
       </c>
       <c r="J47" s="10">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K47" s="10">
         <v>0</v>
       </c>
       <c r="L47" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M47" s="11"/>
       <c r="N47" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="10">
+        <v>6</v>
+      </c>
+      <c r="B48" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="C48" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="D48" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="E48" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="F48" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="G48" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="H48" s="12">
+        <v>46281</v>
+      </c>
+      <c r="I48" s="12">
+        <v>46310</v>
+      </c>
+      <c r="J48" s="10">
+        <v>30</v>
+      </c>
+      <c r="K48" s="10">
+        <v>0</v>
+      </c>
+      <c r="L48" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="M48" s="11"/>
+      <c r="N48" s="10" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -3157,10 +3232,10 @@
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="list" sqref="L4:L47" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" sqref="L4:L48" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Pendiente,En Progreso,Completado,Bloqueado,En Revisión"</formula1>
     </dataValidation>
-    <dataValidation type="whole" sqref="K4:K47" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="whole" sqref="K4:K48" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>0</formula1>
       <formula2>100</formula2>
     </dataValidation>
@@ -3183,50 +3258,50 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>144</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>148</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>150</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>152</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>153</v>
       </c>
     </row>
   </sheetData>
